--- a/AdvanceExcel/Goal Seek 2.xlsx
+++ b/AdvanceExcel/Goal Seek 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Practice\For Golu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE956A4F-93D1-4B40-9508-90E1EB9D6138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8F5D19-DC7F-4F06-A8F7-0D016FBB2A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{37CE435D-A939-45EC-9E9D-08C618BF0025}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{37CE435D-A939-45EC-9E9D-08C618BF0025}"/>
   </bookViews>
   <sheets>
     <sheet name="LoanAmount" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Investment Growth" sheetId="3" r:id="rId3"/>
     <sheet name="Discount Pricing" sheetId="4" r:id="rId4"/>
     <sheet name="Savings Plan" sheetId="5" r:id="rId5"/>
+    <sheet name="Distance" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Annual Rate of Interest</t>
   </si>
@@ -115,6 +116,27 @@
   </si>
   <si>
     <t>Rate Monthly</t>
+  </si>
+  <si>
+    <t>Time Maria Drives</t>
+  </si>
+  <si>
+    <t>Maria Speed</t>
+  </si>
+  <si>
+    <t>Time Edmund Drives</t>
+  </si>
+  <si>
+    <t>Emund Distance</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>Emund Speed</t>
+  </si>
+  <si>
+    <t>Maria Distnace</t>
   </si>
 </sst>
 </file>
@@ -124,8 +146,8 @@
   <numFmts count="4">
     <numFmt numFmtId="6" formatCode="&quot;₹&quot;\ #,##0;[Red]&quot;₹&quot;\ \-#,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="&quot;₹&quot;\ #,##0.0;[Red]&quot;₹&quot;\ \-#,##0.0"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.0;[Red]&quot;₹&quot;\ \-#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -185,14 +207,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -201,7 +223,8 @@
     <xf numFmtId="10" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,4 +829,103 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9967F14-C217-45C8-9824-D588141E8973}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="8">
+        <v>10.000000000000004</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="1">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="1">
+        <f>B1-2</f>
+        <v>8.0000000000000036</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D2:D6" ca="1" si="0">_xlfn.FORMULATEXT(B3)</f>
+        <v>=B1-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1">
+        <v>80</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1">
+        <f>B2*B1</f>
+        <v>640.00000000000023</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=B2*B1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1">
+        <f>B4*B3</f>
+        <v>640.00000000000023</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=B4*B3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8">
+        <f>B5-B6</f>
+        <v>0</v>
+      </c>
+      <c r="D7" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B7)</f>
+        <v>=B5-B6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>